--- a/public/Assets/Files/template_import.xlsx
+++ b/public/Assets/Files/template_import.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\laragon\www\inventaris\public\Assets\Files\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9E0E57EB-B517-43D7-9BFC-7FDB3A860F3F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{35610122-AF9A-4CC5-9189-9F1214437DE0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2256" yWindow="2244" windowWidth="18024" windowHeight="9768" xr2:uid="{6395F108-DA91-4FD0-9FB2-0BE50007F426}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" xr2:uid="{6395F108-DA91-4FD0-9FB2-0BE50007F426}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="30" uniqueCount="19">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="24" uniqueCount="20">
   <si>
     <t>nama_inventaris</t>
   </si>
@@ -48,24 +48,6 @@
     <t>tgl_perolehan_inventaris</t>
   </si>
   <si>
-    <t>Meja</t>
-  </si>
-  <si>
-    <t>Meja Siswa</t>
-  </si>
-  <si>
-    <t>Meja 1</t>
-  </si>
-  <si>
-    <t>Kelas X Kartini 1</t>
-  </si>
-  <si>
-    <t>-</t>
-  </si>
-  <si>
-    <t>Dana BOS</t>
-  </si>
-  <si>
     <t>qty</t>
   </si>
   <si>
@@ -75,20 +57,41 @@
     <t>RIM</t>
   </si>
   <si>
-    <t>Meja 2</t>
-  </si>
-  <si>
-    <t>Kelas X Kartini 2</t>
-  </si>
-  <si>
     <t>Rim</t>
+  </si>
+  <si>
+    <t>Komputer</t>
+  </si>
+  <si>
+    <t>All In One(AIO)</t>
+  </si>
+  <si>
+    <t>Komuter LAB C 1</t>
+  </si>
+  <si>
+    <t>Komuter LAB C 2</t>
+  </si>
+  <si>
+    <t>LAB. Komp. C</t>
+  </si>
+  <si>
+    <t>Intel Core I3-7130U, 4gb RAM, 1000gb HHD</t>
+  </si>
+  <si>
+    <t>Bantuan</t>
+  </si>
+  <si>
+    <t>Bantua</t>
+  </si>
+  <si>
+    <t>harga</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -104,14 +107,20 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="12"/>
-      <color theme="2" tint="-9.9978637043366805E-2"/>
+      <sz val="8"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="8"/>
+      <sz val="12"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color theme="0" tint="-0.14999847407452621"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -137,18 +146,21 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="14" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
@@ -465,20 +477,20 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{143A98E2-015C-43DB-B1CD-5A1F2F3ECD3F}">
-  <dimension ref="A1:I4"/>
+  <dimension ref="A1:J3"/>
   <sheetFormatPr defaultRowHeight="15.6" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="14.5546875" style="4" customWidth="1"/>
-    <col min="2" max="2" width="11.5546875" style="4" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="15.88671875" style="4" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="15.109375" style="4" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="10.33203125" style="4" bestFit="1" customWidth="1"/>
-    <col min="6" max="7" width="10.33203125" style="4" customWidth="1"/>
-    <col min="8" max="8" width="23.6640625" style="4" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="17.88671875" style="4" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="14.5546875" style="2" customWidth="1"/>
+    <col min="2" max="2" width="23.44140625" style="2" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="17.77734375" style="2" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="15.109375" style="2" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="41.44140625" style="2" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="10.33203125" style="2" customWidth="1"/>
+    <col min="8" max="8" width="24.6640625" style="2" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="18.5546875" style="2" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>2</v>
       </c>
@@ -495,10 +507,10 @@
         <v>4</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="H1" s="1" t="s">
         <v>6</v>
@@ -506,96 +518,70 @@
       <c r="I1" s="1" t="s">
         <v>5</v>
       </c>
+      <c r="J1" s="1" t="s">
+        <v>19</v>
+      </c>
     </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A2" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="B2" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="C2" s="2" t="s">
+    <row r="2" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A2" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="B2" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="C2" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="D2" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="E2" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="F2" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="D2" s="2" t="s">
+      <c r="G2" s="4">
+        <v>1</v>
+      </c>
+      <c r="H2" s="5">
+        <v>44084</v>
+      </c>
+      <c r="I2" s="4" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="3" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A3" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="B3" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="C3" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="D3" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="E3" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="F3" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="E2" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="F2" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="G2" s="2">
+      <c r="G3" s="4">
         <v>1</v>
       </c>
-      <c r="H2" s="3">
-        <v>45536</v>
-      </c>
-      <c r="I2" s="2" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A3" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="B3" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="C3" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="D3" s="2" t="s">
+      <c r="H3" s="5">
+        <v>44084</v>
+      </c>
+      <c r="I3" s="4" t="s">
         <v>17</v>
-      </c>
-      <c r="E3" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="F3" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="G3" s="2">
-        <v>2</v>
-      </c>
-      <c r="H3" s="3">
-        <v>45537</v>
-      </c>
-      <c r="I3" s="2" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A4" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="B4" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="C4" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D4" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="E4" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="F4" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="G4" s="2">
-        <v>1</v>
-      </c>
-      <c r="H4" s="3">
-        <v>45536</v>
-      </c>
-      <c r="I4" s="2" t="s">
-        <v>12</v>
       </c>
     </row>
   </sheetData>
-  <phoneticPr fontId="3" type="noConversion"/>
+  <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>